--- a/Daily/Daily G2 - Corte 28 abril.xlsx
+++ b/Daily/Daily G2 - Corte 28 abril.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unisabanaedu-my.sharepoint.com/personal/yosimardiamo_unisabana_edu_co/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andis\prototype-hug\Daily\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D040D1B-E8FF-4E2A-9343-49ACA73E10EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A40F048-D7BC-4EA9-8A0F-7F7B2276DF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9318DF84-4FC1-47D8-9DDA-80712E18598E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9318DF84-4FC1-47D8-9DDA-80712E18598E}"/>
   </bookViews>
   <sheets>
     <sheet name="Grupo 2" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
   <si>
     <t>Fase</t>
   </si>
@@ -237,6 +237,27 @@
   </si>
   <si>
     <t>Canal abierto para reporte de errores del usuario.</t>
+  </si>
+  <si>
+    <t>SEMANA 27 ABR - 3 MAYO</t>
+  </si>
+  <si>
+    <t>SEMANA 4 -10 MAYO</t>
+  </si>
+  <si>
+    <t>SEMANA 11-17 MAYO</t>
+  </si>
+  <si>
+    <t>SEMANA 18-24 MAYO</t>
+  </si>
+  <si>
+    <t>OK (27 Abril)</t>
+  </si>
+  <si>
+    <t>OK (28 Abril)</t>
+  </si>
+  <si>
+    <t>OK (3 Mayo)</t>
   </si>
 </sst>
 </file>
@@ -273,7 +294,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -333,29 +354,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -637,19 +696,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE83B71-19F8-4190-8672-7E17951839F8}">
-  <dimension ref="B1:G24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:K24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -665,337 +725,447 @@
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="H2" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="2"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="2"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="2:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5"/>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="6"/>
-      <c r="C6" s="3" t="s">
+      <c r="H5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="4"/>
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" spans="2:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="2:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5"/>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="6"/>
-      <c r="C9" s="3" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="2:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="4"/>
+      <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+      <c r="H9" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+    </row>
+    <row r="10" spans="2:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" spans="2:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="2:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+    </row>
+    <row r="12" spans="2:11" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="5"/>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="6"/>
-      <c r="C13" s="3" t="s">
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="2:11" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="4"/>
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+      <c r="H13" s="9"/>
+      <c r="I13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+    </row>
+    <row r="14" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+    </row>
+    <row r="15" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="5"/>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="6"/>
-      <c r="C16" s="3" t="s">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+    </row>
+    <row r="16" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="4"/>
+      <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+    </row>
+    <row r="17" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+    </row>
+    <row r="18" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="6"/>
-      <c r="C19" s="3" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+    </row>
+    <row r="19" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="4"/>
+      <c r="C19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="5"/>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="6"/>
-      <c r="C22" s="3" t="s">
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="4"/>
+      <c r="C22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="2" t="s">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="2:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="6"/>
-      <c r="C24" s="3" t="s">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="4"/>
+      <c r="C24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="7">
